--- a/public/employees.xlsx
+++ b/public/employees.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\React\Lucky\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Code\Lucky\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04DF263-C792-477A-AE65-44678173E2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604F297D-706B-4480-B40B-D87A95135E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{70EF5747-069E-4E0B-A6D6-A2157A90F64C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{70EF5747-069E-4E0B-A6D6-A2157A90F64C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
-  <si>
-    <t>Họ tên</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="94">
   <si>
     <t>Phạm Trung Kiên</t>
   </si>
@@ -86,15 +83,9 @@
     <t>Ninh Công Minh</t>
   </si>
   <si>
-    <t>Mr. Minh's Son</t>
-  </si>
-  <si>
     <t>Ngô Khoa Văn</t>
   </si>
   <si>
-    <t>Vợ Mr. Văn</t>
-  </si>
-  <si>
     <t>Phạm Thị Thúy Mai</t>
   </si>
   <si>
@@ -122,12 +113,6 @@
     <t>Lee Joonpeel</t>
   </si>
   <si>
-    <t>Choi Gyeonghui</t>
-  </si>
-  <si>
-    <t>Lee Roun</t>
-  </si>
-  <si>
     <t>Nguyễn Hồng Vân</t>
   </si>
   <si>
@@ -185,20 +170,162 @@
     <t>Nguyễn Đức Thành</t>
   </si>
   <si>
-    <t>Vợ Mr. Thành</t>
-  </si>
-  <si>
     <t>Nguyễn Thanh Tùng (COSCO)</t>
   </si>
   <si>
     <t>Nguyễn Thanh Tùng (KMTC)</t>
+  </si>
+  <si>
+    <t>Nam/ Nữ</t>
+  </si>
+  <si>
+    <t>Tên</t>
+  </si>
+  <si>
+    <t>Chức danh</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Managing Director Vietnam</t>
+  </si>
+  <si>
+    <t>Sales Manager</t>
+  </si>
+  <si>
+    <t>Operations Team Leader</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Deputy Manager, Logistics Department</t>
+  </si>
+  <si>
+    <t>North Vietnam Director</t>
+  </si>
+  <si>
+    <t>Branch Manager</t>
+  </si>
+  <si>
+    <t>Hai Phong Branch Manager</t>
+  </si>
+  <si>
+    <t>OPD Team Leader</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>Deputy General Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocean Operations Manager - Vietnam; 
+Intra-Asia, Asia Pacific Operations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hanoi Branch Manager/ Commercial Manager </t>
+  </si>
+  <si>
+    <t>Ms.</t>
+  </si>
+  <si>
+    <t>North Branch Manager</t>
+  </si>
+  <si>
+    <t>Logistics Manager</t>
+  </si>
+  <si>
+    <t>North Documentation Manager</t>
+  </si>
+  <si>
+    <t>General Manager (HN &amp; HP Branch)</t>
+  </si>
+  <si>
+    <t>Northern KMTC VN Manager</t>
+  </si>
+  <si>
+    <t>Vice Director KMTC HP Branch</t>
+  </si>
+  <si>
+    <t>Owner Representative</t>
+  </si>
+  <si>
+    <t>Mrs.</t>
+  </si>
+  <si>
+    <t>Phó Chủ tịch HĐTV</t>
+  </si>
+  <si>
+    <t>Thành viên HĐTV</t>
+  </si>
+  <si>
+    <t>Trưởng ban Thư kí tổng hợp</t>
+  </si>
+  <si>
+    <t>Phó Trưởng Ban Cảng biển &amp; Dịch vụ Hàng hải</t>
+  </si>
+  <si>
+    <t>Chủ tịch HĐQT</t>
+  </si>
+  <si>
+    <t>Phó Chủ tịch HĐQT</t>
+  </si>
+  <si>
+    <t>Phó Tổng Giám đốc</t>
+  </si>
+  <si>
+    <t>Phó Bí thư thường trực Đảng ủy</t>
+  </si>
+  <si>
+    <t>Phó Chi cục Trưởng</t>
+  </si>
+  <si>
+    <t>Đội trưởng</t>
+  </si>
+  <si>
+    <t>Đội phó</t>
+  </si>
+  <si>
+    <t>Chỉ huy trưởng</t>
+  </si>
+  <si>
+    <t>Tổ trưởng tổ nghiệp vụ Lạch Huyện</t>
+  </si>
+  <si>
+    <t>Giám đốc</t>
+  </si>
+  <si>
+    <t>Trưởng đại diện</t>
+  </si>
+  <si>
+    <t>Deputy Manager of HP Branch &amp; MSD Team Leader, Cosco Shipping Lines (Vietnam) Co., LTD</t>
+  </si>
+  <si>
+    <t>Terminal Manager - Hai Phong Branch, Zim Integrated Shipping Services (Vietnam) LLC</t>
+  </si>
+  <si>
+    <t>Giám đốc, Cảng vụ Hàng hải Hải Phòng</t>
+  </si>
+  <si>
+    <t>Operation Supervisor, OOCL (Vietnam) Co., LTD</t>
+  </si>
+  <si>
+    <t>Nhóm trưởng, Hải quan cửa khẩu Cảng Đình Vũ</t>
+  </si>
+  <si>
+    <t>General Manager, Sinotrans Container Lines (Vietnam) Company Limited</t>
+  </si>
+  <si>
+    <t>HPH Manager, T.S. Container Lines  Ha Noi Co., LTD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,7 +347,19 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -235,18 +374,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -254,28 +393,77 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{8FC950B1-1F9D-4744-A60B-32CF006E83C6}"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{E56E280F-67D7-47B7-9E77-D5CF579EB281}"/>
   </cellStyles>
   <dxfs count="6">
@@ -657,299 +845,568 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5326ED1-5381-4F4B-907B-E9EA28CAE53A}">
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" ht="99" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="33" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="33" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="214.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="132" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="33" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="99" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="132" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="66" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="33" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="99" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="33" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>1</v>
+      <c r="C48" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A16 A4:A6 A2">
-    <cfRule type="cellIs" dxfId="5" priority="6" stopIfTrue="1" operator="equal">
+  <mergeCells count="3">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A17:B17 A5:C7 A3:C3 A18 C17:C18 A19:C29">
+    <cfRule type="cellIs" dxfId="5" priority="7" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="cellIs" dxfId="4" priority="5" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="A4:C4">
+    <cfRule type="cellIs" dxfId="4" priority="6" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A8">
-    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="A8:C9">
+    <cfRule type="cellIs" dxfId="3" priority="5" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A34:A37 A9:A32">
-    <cfRule type="cellIs" dxfId="2" priority="3" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="A31:C34 A18:B18 A10:C17">
+    <cfRule type="cellIs" dxfId="2" priority="4" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A33">
+  <conditionalFormatting sqref="A30:C30">
     <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A38:A41">
+  <conditionalFormatting sqref="A35:C38">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
